--- a/Sindhi Muslim/Student Attendance/Class 3/Class 3 - Monthly Attendance - October-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/Class 3/Class 3 - Monthly Attendance - October-2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Student Attendance\Class 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\Class 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D25546-B90D-46AE-9BEB-288F61A00F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46D130F-34C3-4760-9A71-398BD584DBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class-III (Boys)" sheetId="7" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="132">
   <si>
     <t>S.No</t>
   </si>
@@ -419,6 +419,18 @@
   </si>
   <si>
     <t>Monthly Attendence Month of October-2024</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>PTM -PTM - PTM - PTM - PTM</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -502,7 +514,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -518,6 +530,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,7 +662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -694,24 +712,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -724,8 +724,38 @@
     <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1252,99 +1282,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="33"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="30" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1471,25 +1501,25 @@
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="29" t="s">
+      <c r="AK3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="29" t="s">
+      <c r="AL3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="30" t="s">
+      <c r="AM3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="31"/>
+      <c r="AN3" s="25"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="21">
         <v>45566</v>
       </c>
@@ -1583,8 +1613,8 @@
       <c r="AJ4" s="21">
         <v>45596</v>
       </c>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29"/>
+      <c r="AK4" s="23"/>
+      <c r="AL4" s="23"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1610,48 +1640,102 @@
       <c r="E5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="23" t="s">
+      <c r="F5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J5" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="23" t="s">
+      <c r="L5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R5" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="23" t="s">
+      <c r="S5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y5" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="23" t="s">
+      <c r="Z5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF5" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="22"/>
-      <c r="AJ5" s="11"/>
+      <c r="AG5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ5" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK33" si="2">COUNTIF(F5:AJ5,"P")</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL5" s="5">
         <f t="shared" ref="AL5:AL33" si="3">COUNTIF(F5:AJ5,"A")</f>
@@ -1666,7 +1750,7 @@
       <c r="AO5" s="13"/>
       <c r="AP5" s="3"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1682,44 +1766,96 @@
       <c r="E6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="22"/>
-      <c r="AJ6" s="11"/>
+      <c r="F6" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="36"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R6" s="28"/>
+      <c r="S6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ6" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM6" s="5" t="s">
         <v>10</v>
@@ -1730,7 +1866,7 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -1746,51 +1882,103 @@
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="22"/>
-      <c r="AJ7" s="11"/>
+      <c r="F7" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="36"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R7" s="28"/>
+      <c r="S7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC7" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ7" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL7" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -1806,53 +1994,105 @@
       <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="22"/>
-      <c r="AJ8" s="11"/>
+      <c r="F8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" s="36"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" s="28"/>
+      <c r="S8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ8" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL8" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AN8" s="31"/>
-      <c r="AO8" s="31"/>
-      <c r="AP8" s="32"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="25"/>
+      <c r="AP8" s="26"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -1868,40 +2108,92 @@
       <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="22"/>
-      <c r="AJ9" s="11"/>
+      <c r="F9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="36"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R9" s="28"/>
+      <c r="S9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ9" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL9" s="5">
         <f t="shared" si="3"/>
@@ -1920,7 +2212,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -1936,40 +2228,92 @@
       <c r="E10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="11"/>
-      <c r="AH10" s="11"/>
-      <c r="AI10" s="22"/>
-      <c r="AJ10" s="11"/>
+      <c r="F10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J10" s="36"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R10" s="28"/>
+      <c r="S10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF10" s="28"/>
+      <c r="AG10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ10" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="3"/>
@@ -1991,7 +2335,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -2007,62 +2351,114 @@
       <c r="E11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="11"/>
-      <c r="AH11" s="11"/>
-      <c r="AI11" s="22"/>
-      <c r="AJ11" s="11"/>
+      <c r="F11" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="36"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R11" s="28"/>
+      <c r="S11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE11" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ11" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="AN11" s="12">
         <f>AK6+AK7+AK8+AK11+AK12+AK13+AK15+AK19+AK20+AK21+AK22+AK23+AK24+AK25+AK26+AK28+AK29+AK31</f>
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="AO11" s="12">
         <f>AK5+AK9+AK10+AK14+AK16+AK17+AK18+AK27+AK30+AK32</f>
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="AP11" s="12">
         <f>AN11+AO11</f>
-        <v>0</v>
+        <v>584</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>8</v>
       </c>
@@ -2078,62 +2474,114 @@
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="11"/>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="22"/>
-      <c r="AJ12" s="11"/>
+      <c r="F12" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J12" s="36"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R12" s="28"/>
+      <c r="S12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ12" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0</v>
+        <v>0.71052631578947367</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0</v>
+        <v>0.42673992673992672</v>
       </c>
       <c r="AP12" s="12">
         <f>AP11/AP10</f>
-        <v>0</v>
+        <v>0.56153846153846154</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -2149,51 +2597,103 @@
       <c r="E13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="11"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="22"/>
-      <c r="AJ13" s="11"/>
+      <c r="F13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="36"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R13" s="28"/>
+      <c r="S13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI13" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ13" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AM13" s="3"/>
       <c r="AN13" s="17"/>
       <c r="AO13" s="17"/>
       <c r="AP13" s="17"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -2209,51 +2709,103 @@
       <c r="E14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="11"/>
-      <c r="AH14" s="11"/>
-      <c r="AI14" s="22"/>
-      <c r="AJ14" s="11"/>
+      <c r="F14" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="36"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R14" s="28"/>
+      <c r="S14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ14" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL14" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AM14" s="19"/>
       <c r="AN14" s="19"/>
       <c r="AO14" s="19"/>
       <c r="AP14" s="19"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -2269,51 +2821,103 @@
       <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="22"/>
-      <c r="AJ15" s="11"/>
+      <c r="F15" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J15" s="36"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R15" s="28"/>
+      <c r="S15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ15" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL15" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>12</v>
       </c>
@@ -2329,53 +2933,105 @@
       <c r="E16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="11"/>
-      <c r="AH16" s="11"/>
-      <c r="AI16" s="22"/>
-      <c r="AJ16" s="11"/>
+      <c r="F16" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="36"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R16" s="28"/>
+      <c r="S16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ16" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL16" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="31"/>
-      <c r="AO16" s="31"/>
-      <c r="AP16" s="32"/>
+      <c r="AM16" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN16" s="25"/>
+      <c r="AO16" s="25"/>
+      <c r="AP16" s="26"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -2391,44 +3047,96 @@
       <c r="E17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="11"/>
-      <c r="AH17" s="11"/>
-      <c r="AI17" s="22"/>
-      <c r="AJ17" s="11"/>
+      <c r="F17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="36"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R17" s="28"/>
+      <c r="S17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ17" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL17" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM17" s="5" t="s">
         <v>12</v>
@@ -2443,7 +3151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>14</v>
       </c>
@@ -2459,44 +3167,96 @@
       <c r="E18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="11"/>
-      <c r="AH18" s="11"/>
-      <c r="AI18" s="22"/>
-      <c r="AJ18" s="11"/>
+      <c r="F18" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J18" s="36"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R18" s="28"/>
+      <c r="S18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD18" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ18" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL18" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" s="5" t="s">
         <v>16</v>
@@ -2514,7 +3274,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -2530,40 +3290,92 @@
       <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="22"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="22"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="22"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="11"/>
-      <c r="AH19" s="11"/>
-      <c r="AI19" s="22"/>
-      <c r="AJ19" s="11"/>
+      <c r="F19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J19" s="36"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R19" s="28"/>
+      <c r="S19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF19" s="28"/>
+      <c r="AG19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ19" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="3"/>
@@ -2574,18 +3386,18 @@
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>494</v>
+        <v>143</v>
       </c>
       <c r="AO19" s="12">
         <f>AO18-AO11</f>
-        <v>546</v>
+        <v>313</v>
       </c>
       <c r="AP19" s="12">
         <f>AN19+AO19</f>
-        <v>1040</v>
+        <v>456</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>16</v>
       </c>
@@ -2601,62 +3413,114 @@
       <c r="E20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="22"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="22"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="11"/>
-      <c r="AH20" s="11"/>
-      <c r="AI20" s="22"/>
-      <c r="AJ20" s="11"/>
+      <c r="F20" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="36"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R20" s="28"/>
+      <c r="S20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE20" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF20" s="28"/>
+      <c r="AG20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ20" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL20" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>1</v>
+        <v>0.28947368421052633</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>1</v>
+        <v>0.57326007326007322</v>
       </c>
       <c r="AP20" s="20">
         <f>AP19/AP18</f>
-        <v>1</v>
+        <v>0.43846153846153846</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -2672,47 +3536,99 @@
       <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="11"/>
-      <c r="AD21" s="11"/>
-      <c r="AE21" s="11"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="11"/>
-      <c r="AH21" s="11"/>
-      <c r="AI21" s="22"/>
-      <c r="AJ21" s="11"/>
+      <c r="F21" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="36"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R21" s="28"/>
+      <c r="S21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="V21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y21" s="28"/>
+      <c r="Z21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF21" s="28"/>
+      <c r="AG21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ21" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AL21" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>18</v>
       </c>
@@ -2728,47 +3644,99 @@
       <c r="E22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="24"/>
-      <c r="AG22" s="11"/>
-      <c r="AH22" s="11"/>
-      <c r="AI22" s="22"/>
-      <c r="AJ22" s="11"/>
+      <c r="F22" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J22" s="36"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R22" s="28"/>
+      <c r="S22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y22" s="28"/>
+      <c r="Z22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF22" s="28"/>
+      <c r="AG22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ22" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL22" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -2784,47 +3752,99 @@
       <c r="E23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="24"/>
-      <c r="AG23" s="11"/>
-      <c r="AH23" s="11"/>
-      <c r="AI23" s="22"/>
-      <c r="AJ23" s="11"/>
+      <c r="F23" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="36"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R23" s="28"/>
+      <c r="S23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF23" s="28"/>
+      <c r="AG23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ23" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL23" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>20</v>
       </c>
@@ -2840,47 +3860,99 @@
       <c r="E24" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="22"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="22"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="11"/>
-      <c r="AD24" s="11"/>
-      <c r="AE24" s="11"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="11"/>
-      <c r="AH24" s="11"/>
-      <c r="AI24" s="22"/>
-      <c r="AJ24" s="11"/>
+      <c r="F24" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="36"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R24" s="28"/>
+      <c r="S24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y24" s="28"/>
+      <c r="Z24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE24" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF24" s="28"/>
+      <c r="AG24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ24" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL24" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -2896,47 +3968,99 @@
       <c r="E25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="22"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="11"/>
-      <c r="AD25" s="11"/>
-      <c r="AE25" s="11"/>
-      <c r="AF25" s="24"/>
-      <c r="AG25" s="11"/>
-      <c r="AH25" s="11"/>
-      <c r="AI25" s="22"/>
-      <c r="AJ25" s="11"/>
+      <c r="F25" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="36"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R25" s="28"/>
+      <c r="S25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA25" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE25" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF25" s="28"/>
+      <c r="AG25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ25" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL25" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>22</v>
       </c>
@@ -2952,47 +4076,99 @@
       <c r="E26" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="22"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="22"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="11"/>
-      <c r="AD26" s="11"/>
-      <c r="AE26" s="11"/>
-      <c r="AF26" s="24"/>
-      <c r="AG26" s="11"/>
-      <c r="AH26" s="11"/>
-      <c r="AI26" s="22"/>
-      <c r="AJ26" s="11"/>
+      <c r="F26" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J26" s="36"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R26" s="28"/>
+      <c r="S26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF26" s="28"/>
+      <c r="AG26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ26" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL26" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -3008,47 +4184,99 @@
       <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="22"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="24"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="22"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="11"/>
-      <c r="AD27" s="11"/>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="24"/>
-      <c r="AG27" s="11"/>
-      <c r="AH27" s="11"/>
-      <c r="AI27" s="22"/>
-      <c r="AJ27" s="11"/>
+      <c r="F27" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="36"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R27" s="28"/>
+      <c r="S27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ27" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL27" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>24</v>
       </c>
@@ -3064,47 +4292,99 @@
       <c r="E28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="22"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="11"/>
-      <c r="AD28" s="11"/>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="24"/>
-      <c r="AG28" s="11"/>
-      <c r="AH28" s="11"/>
-      <c r="AI28" s="22"/>
-      <c r="AJ28" s="11"/>
+      <c r="F28" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J28" s="36"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R28" s="28"/>
+      <c r="S28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF28" s="28"/>
+      <c r="AG28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ28" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL28" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>25</v>
       </c>
@@ -3120,47 +4400,99 @@
       <c r="E29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="22"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="11"/>
-      <c r="AA29" s="22"/>
-      <c r="AB29" s="11"/>
-      <c r="AC29" s="11"/>
-      <c r="AD29" s="11"/>
-      <c r="AE29" s="11"/>
-      <c r="AF29" s="24"/>
-      <c r="AG29" s="11"/>
-      <c r="AH29" s="11"/>
-      <c r="AI29" s="22"/>
-      <c r="AJ29" s="11"/>
+      <c r="F29" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I29" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J29" s="36"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R29" s="28"/>
+      <c r="S29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF29" s="28"/>
+      <c r="AG29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ29" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK29" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL29" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>26</v>
       </c>
@@ -3176,47 +4508,99 @@
       <c r="E30" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="22"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="24"/>
-      <c r="S30" s="11"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="11"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="11"/>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="11"/>
-      <c r="AC30" s="11"/>
-      <c r="AD30" s="11"/>
-      <c r="AE30" s="11"/>
-      <c r="AF30" s="24"/>
-      <c r="AG30" s="11"/>
-      <c r="AH30" s="11"/>
-      <c r="AI30" s="22"/>
-      <c r="AJ30" s="11"/>
+      <c r="F30" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J30" s="36"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R30" s="28"/>
+      <c r="S30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V30" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W30" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE30" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF30" s="28"/>
+      <c r="AG30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ30" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK30" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL30" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>27</v>
       </c>
@@ -3230,47 +4614,99 @@
       <c r="E31" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="24"/>
-      <c r="S31" s="11"/>
-      <c r="T31" s="22"/>
-      <c r="U31" s="11"/>
-      <c r="V31" s="22"/>
-      <c r="W31" s="11"/>
-      <c r="X31" s="11"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="11"/>
-      <c r="AA31" s="22"/>
-      <c r="AB31" s="11"/>
-      <c r="AC31" s="11"/>
-      <c r="AD31" s="11"/>
-      <c r="AE31" s="11"/>
-      <c r="AF31" s="24"/>
-      <c r="AG31" s="11"/>
-      <c r="AH31" s="11"/>
-      <c r="AI31" s="22"/>
-      <c r="AJ31" s="11"/>
+      <c r="F31" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="H31" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J31" s="36"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R31" s="28"/>
+      <c r="S31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA31" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF31" s="28"/>
+      <c r="AG31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ31" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK31" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL31" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>28</v>
       </c>
@@ -3284,47 +4720,99 @@
       <c r="E32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="22"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="24"/>
-      <c r="S32" s="11"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="11"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="11"/>
-      <c r="X32" s="11"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="11"/>
-      <c r="AA32" s="22"/>
-      <c r="AB32" s="11"/>
-      <c r="AC32" s="11"/>
-      <c r="AD32" s="11"/>
-      <c r="AE32" s="11"/>
-      <c r="AF32" s="24"/>
-      <c r="AG32" s="11"/>
-      <c r="AH32" s="11"/>
-      <c r="AI32" s="22"/>
-      <c r="AJ32" s="11"/>
+      <c r="F32" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H32" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J32" s="36"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R32" s="28"/>
+      <c r="S32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA32" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF32" s="28"/>
+      <c r="AG32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ32" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK32" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL32" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>29</v>
       </c>
@@ -3338,53 +4826,103 @@
       <c r="E33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="22"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="25"/>
-      <c r="S33" s="11"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="11"/>
-      <c r="V33" s="22"/>
-      <c r="W33" s="11"/>
-      <c r="X33" s="11"/>
-      <c r="Y33" s="25"/>
-      <c r="Z33" s="11"/>
-      <c r="AA33" s="22"/>
-      <c r="AB33" s="11"/>
-      <c r="AC33" s="11"/>
-      <c r="AD33" s="11"/>
-      <c r="AE33" s="11"/>
-      <c r="AF33" s="25"/>
-      <c r="AG33" s="11"/>
-      <c r="AH33" s="11"/>
-      <c r="AI33" s="22"/>
-      <c r="AJ33" s="11"/>
+      <c r="F33" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I33" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J33" s="37"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P33" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R33" s="29"/>
+      <c r="S33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y33" s="29"/>
+      <c r="Z33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF33" s="29"/>
+      <c r="AG33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ33" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK33" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL33" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AN3"/>
-    <mergeCell ref="AM8:AP8"/>
-    <mergeCell ref="AM16:AP16"/>
+  <mergeCells count="17">
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="J5:J33"/>
     <mergeCell ref="Y5:Y33"/>
     <mergeCell ref="AF5:AF33"/>
     <mergeCell ref="K5:K33"/>
@@ -3394,18 +4932,21 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM3:AN3"/>
+    <mergeCell ref="AM8:AP8"/>
+    <mergeCell ref="AM16:AP16"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B33">
     <cfRule type="duplicateValues" dxfId="24" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:M5 R5 T5 V5 Y5 AA5 AF5 AI5 N5:Q33 S5:S33 U5:U33 W5:X33 Z5:Z33 AB5:AE33 AG5:AH33 AJ5:AJ33 G6:J33 L6:L33 F4:AJ4">
+  <conditionalFormatting sqref="F6:I33 L6:Q33 S6:X33 Z6:AE33 F4:AJ5 AG6:AJ33">
     <cfRule type="expression" dxfId="23" priority="15">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:M5 R5 T5 V5 Y5 AA5 AF5 AI5 N5:Q33 S5:S33 U5:U33 W5:X33 Z5:Z33 AB5:AE33 AG5:AH33 AJ5:AJ33 G6:J33 L6:L33">
+  <conditionalFormatting sqref="F6:I33 L6:Q33 S6:X33 Z6:AE33 F5:AJ5 AG6:AJ33">
     <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -3416,7 +4957,7 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AJ4 F5:M5 R5 T5 V5 Y5 AA5 AF5 AI5 N5:Q33 S5:S33 U5:U33 W5:X33 Z5:Z33 AB5:AE33 AG5:AH33 AJ5:AJ33 G6:J33 L6:L33 AM4:AN4">
+  <conditionalFormatting sqref="AM4:AN4 F6:I33 L6:Q33 S6:X33 Z6:AE33 F3:AJ5 AG6:AJ33">
     <cfRule type="expression" dxfId="19" priority="16">
       <formula>F$3="Sun"</formula>
     </cfRule>
@@ -3502,99 +5043,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="26"/>
-      <c r="AB1" s="26"/>
-      <c r="AC1" s="26"/>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="26"/>
-      <c r="AF1" s="26"/>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="33"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="30" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -3721,25 +5262,25 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="29" t="s">
+      <c r="AK3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="29" t="s">
+      <c r="AL3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="30" t="s">
+      <c r="AM3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="31"/>
+      <c r="AN3" s="25"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="21">
         <v>45566</v>
       </c>
@@ -3833,8 +5374,8 @@
       <c r="AJ4" s="21">
         <v>45596</v>
       </c>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29"/>
+      <c r="AK4" s="23"/>
+      <c r="AL4" s="23"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -3865,7 +5406,7 @@
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="27" t="s">
         <v>126</v>
       </c>
       <c r="L5" s="11"/>
@@ -3874,7 +5415,7 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
-      <c r="R5" s="23" t="s">
+      <c r="R5" s="27" t="s">
         <v>126</v>
       </c>
       <c r="S5" s="11"/>
@@ -3883,7 +5424,7 @@
       <c r="V5" s="22"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
-      <c r="Y5" s="23" t="s">
+      <c r="Y5" s="27" t="s">
         <v>126</v>
       </c>
       <c r="Z5" s="11"/>
@@ -3892,7 +5433,7 @@
       <c r="AC5" s="11"/>
       <c r="AD5" s="11"/>
       <c r="AE5" s="11"/>
-      <c r="AF5" s="23" t="s">
+      <c r="AF5" s="27" t="s">
         <v>126</v>
       </c>
       <c r="AG5" s="11"/>
@@ -3939,28 +5480,28 @@
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
-      <c r="K6" s="24"/>
+      <c r="K6" s="28"/>
       <c r="L6" s="11"/>
       <c r="M6" s="22"/>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
-      <c r="R6" s="24"/>
+      <c r="R6" s="28"/>
       <c r="S6" s="11"/>
       <c r="T6" s="22"/>
       <c r="U6" s="11"/>
       <c r="V6" s="22"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
-      <c r="Y6" s="24"/>
+      <c r="Y6" s="28"/>
       <c r="Z6" s="11"/>
       <c r="AA6" s="22"/>
       <c r="AB6" s="11"/>
       <c r="AC6" s="11"/>
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
-      <c r="AF6" s="24"/>
+      <c r="AF6" s="28"/>
       <c r="AG6" s="11"/>
       <c r="AH6" s="11"/>
       <c r="AI6" s="22"/>
@@ -4003,28 +5544,28 @@
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
-      <c r="K7" s="24"/>
+      <c r="K7" s="28"/>
       <c r="L7" s="11"/>
       <c r="M7" s="22"/>
       <c r="N7" s="11"/>
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
-      <c r="R7" s="24"/>
+      <c r="R7" s="28"/>
       <c r="S7" s="11"/>
       <c r="T7" s="22"/>
       <c r="U7" s="11"/>
       <c r="V7" s="22"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
-      <c r="Y7" s="24"/>
+      <c r="Y7" s="28"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="22"/>
       <c r="AB7" s="11"/>
       <c r="AC7" s="11"/>
       <c r="AD7" s="11"/>
       <c r="AE7" s="11"/>
-      <c r="AF7" s="24"/>
+      <c r="AF7" s="28"/>
       <c r="AG7" s="11"/>
       <c r="AH7" s="11"/>
       <c r="AI7" s="22"/>
@@ -4063,28 +5604,28 @@
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
-      <c r="K8" s="24"/>
+      <c r="K8" s="28"/>
       <c r="L8" s="11"/>
       <c r="M8" s="22"/>
       <c r="N8" s="11"/>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
-      <c r="R8" s="24"/>
+      <c r="R8" s="28"/>
       <c r="S8" s="11"/>
       <c r="T8" s="22"/>
       <c r="U8" s="11"/>
       <c r="V8" s="22"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
-      <c r="Y8" s="24"/>
+      <c r="Y8" s="28"/>
       <c r="Z8" s="11"/>
       <c r="AA8" s="22"/>
       <c r="AB8" s="11"/>
       <c r="AC8" s="11"/>
       <c r="AD8" s="11"/>
       <c r="AE8" s="11"/>
-      <c r="AF8" s="24"/>
+      <c r="AF8" s="28"/>
       <c r="AG8" s="11"/>
       <c r="AH8" s="11"/>
       <c r="AI8" s="22"/>
@@ -4097,12 +5638,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AM8" s="30" t="s">
+      <c r="AM8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AN8" s="31"/>
-      <c r="AO8" s="31"/>
-      <c r="AP8" s="32"/>
+      <c r="AN8" s="25"/>
+      <c r="AO8" s="25"/>
+      <c r="AP8" s="26"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -4125,28 +5666,28 @@
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
-      <c r="K9" s="24"/>
+      <c r="K9" s="28"/>
       <c r="L9" s="11"/>
       <c r="M9" s="22"/>
       <c r="N9" s="11"/>
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
-      <c r="R9" s="24"/>
+      <c r="R9" s="28"/>
       <c r="S9" s="11"/>
       <c r="T9" s="22"/>
       <c r="U9" s="11"/>
       <c r="V9" s="22"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
-      <c r="Y9" s="24"/>
+      <c r="Y9" s="28"/>
       <c r="Z9" s="11"/>
       <c r="AA9" s="22"/>
       <c r="AB9" s="11"/>
       <c r="AC9" s="11"/>
       <c r="AD9" s="11"/>
       <c r="AE9" s="11"/>
-      <c r="AF9" s="24"/>
+      <c r="AF9" s="28"/>
       <c r="AG9" s="11"/>
       <c r="AH9" s="11"/>
       <c r="AI9" s="22"/>
@@ -4193,28 +5734,28 @@
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
-      <c r="K10" s="24"/>
+      <c r="K10" s="28"/>
       <c r="L10" s="11"/>
       <c r="M10" s="22"/>
       <c r="N10" s="11"/>
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
-      <c r="R10" s="24"/>
+      <c r="R10" s="28"/>
       <c r="S10" s="11"/>
       <c r="T10" s="22"/>
       <c r="U10" s="11"/>
       <c r="V10" s="22"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
-      <c r="Y10" s="24"/>
+      <c r="Y10" s="28"/>
       <c r="Z10" s="11"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="11"/>
       <c r="AC10" s="11"/>
       <c r="AD10" s="11"/>
       <c r="AE10" s="11"/>
-      <c r="AF10" s="24"/>
+      <c r="AF10" s="28"/>
       <c r="AG10" s="11"/>
       <c r="AH10" s="11"/>
       <c r="AI10" s="22"/>
@@ -4264,28 +5805,28 @@
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
-      <c r="K11" s="24"/>
+      <c r="K11" s="28"/>
       <c r="L11" s="11"/>
       <c r="M11" s="22"/>
       <c r="N11" s="11"/>
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
-      <c r="R11" s="24"/>
+      <c r="R11" s="28"/>
       <c r="S11" s="11"/>
       <c r="T11" s="22"/>
       <c r="U11" s="11"/>
       <c r="V11" s="22"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
-      <c r="Y11" s="24"/>
+      <c r="Y11" s="28"/>
       <c r="Z11" s="11"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="11"/>
       <c r="AC11" s="11"/>
       <c r="AD11" s="11"/>
       <c r="AE11" s="11"/>
-      <c r="AF11" s="24"/>
+      <c r="AF11" s="28"/>
       <c r="AG11" s="11"/>
       <c r="AH11" s="11"/>
       <c r="AI11" s="22"/>
@@ -4335,28 +5876,28 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
-      <c r="K12" s="24"/>
+      <c r="K12" s="28"/>
       <c r="L12" s="11"/>
       <c r="M12" s="22"/>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
-      <c r="R12" s="24"/>
+      <c r="R12" s="28"/>
       <c r="S12" s="11"/>
       <c r="T12" s="22"/>
       <c r="U12" s="11"/>
       <c r="V12" s="22"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
-      <c r="Y12" s="24"/>
+      <c r="Y12" s="28"/>
       <c r="Z12" s="11"/>
       <c r="AA12" s="22"/>
       <c r="AB12" s="11"/>
       <c r="AC12" s="11"/>
       <c r="AD12" s="11"/>
       <c r="AE12" s="11"/>
-      <c r="AF12" s="24"/>
+      <c r="AF12" s="28"/>
       <c r="AG12" s="11"/>
       <c r="AH12" s="11"/>
       <c r="AI12" s="22"/>
@@ -4406,28 +5947,28 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
-      <c r="K13" s="24"/>
+      <c r="K13" s="28"/>
       <c r="L13" s="11"/>
       <c r="M13" s="22"/>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
-      <c r="R13" s="24"/>
+      <c r="R13" s="28"/>
       <c r="S13" s="11"/>
       <c r="T13" s="22"/>
       <c r="U13" s="11"/>
       <c r="V13" s="22"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
-      <c r="Y13" s="24"/>
+      <c r="Y13" s="28"/>
       <c r="Z13" s="11"/>
       <c r="AA13" s="22"/>
       <c r="AB13" s="11"/>
       <c r="AC13" s="11"/>
       <c r="AD13" s="11"/>
       <c r="AE13" s="11"/>
-      <c r="AF13" s="24"/>
+      <c r="AF13" s="28"/>
       <c r="AG13" s="11"/>
       <c r="AH13" s="11"/>
       <c r="AI13" s="22"/>
@@ -4466,28 +6007,28 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
-      <c r="K14" s="24"/>
+      <c r="K14" s="28"/>
       <c r="L14" s="11"/>
       <c r="M14" s="22"/>
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
-      <c r="R14" s="24"/>
+      <c r="R14" s="28"/>
       <c r="S14" s="11"/>
       <c r="T14" s="22"/>
       <c r="U14" s="11"/>
       <c r="V14" s="22"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
-      <c r="Y14" s="24"/>
+      <c r="Y14" s="28"/>
       <c r="Z14" s="11"/>
       <c r="AA14" s="22"/>
       <c r="AB14" s="11"/>
       <c r="AC14" s="11"/>
       <c r="AD14" s="11"/>
       <c r="AE14" s="11"/>
-      <c r="AF14" s="24"/>
+      <c r="AF14" s="28"/>
       <c r="AG14" s="11"/>
       <c r="AH14" s="11"/>
       <c r="AI14" s="22"/>
@@ -4526,28 +6067,28 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
-      <c r="K15" s="24"/>
+      <c r="K15" s="28"/>
       <c r="L15" s="11"/>
       <c r="M15" s="22"/>
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
-      <c r="R15" s="24"/>
+      <c r="R15" s="28"/>
       <c r="S15" s="11"/>
       <c r="T15" s="22"/>
       <c r="U15" s="11"/>
       <c r="V15" s="22"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="28"/>
       <c r="Z15" s="11"/>
       <c r="AA15" s="22"/>
       <c r="AB15" s="11"/>
       <c r="AC15" s="11"/>
       <c r="AD15" s="11"/>
       <c r="AE15" s="11"/>
-      <c r="AF15" s="24"/>
+      <c r="AF15" s="28"/>
       <c r="AG15" s="11"/>
       <c r="AH15" s="11"/>
       <c r="AI15" s="22"/>
@@ -4586,28 +6127,28 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
-      <c r="K16" s="24"/>
+      <c r="K16" s="28"/>
       <c r="L16" s="11"/>
       <c r="M16" s="22"/>
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
-      <c r="R16" s="24"/>
+      <c r="R16" s="28"/>
       <c r="S16" s="11"/>
       <c r="T16" s="22"/>
       <c r="U16" s="11"/>
       <c r="V16" s="22"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
-      <c r="Y16" s="24"/>
+      <c r="Y16" s="28"/>
       <c r="Z16" s="11"/>
       <c r="AA16" s="22"/>
       <c r="AB16" s="11"/>
       <c r="AC16" s="11"/>
       <c r="AD16" s="11"/>
       <c r="AE16" s="11"/>
-      <c r="AF16" s="24"/>
+      <c r="AF16" s="28"/>
       <c r="AG16" s="11"/>
       <c r="AH16" s="11"/>
       <c r="AI16" s="22"/>
@@ -4620,12 +6161,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AM16" s="30" t="s">
+      <c r="AM16" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="31"/>
-      <c r="AO16" s="31"/>
-      <c r="AP16" s="32"/>
+      <c r="AN16" s="25"/>
+      <c r="AO16" s="25"/>
+      <c r="AP16" s="26"/>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -4648,28 +6189,28 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
-      <c r="K17" s="24"/>
+      <c r="K17" s="28"/>
       <c r="L17" s="11"/>
       <c r="M17" s="22"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
-      <c r="R17" s="24"/>
+      <c r="R17" s="28"/>
       <c r="S17" s="11"/>
       <c r="T17" s="22"/>
       <c r="U17" s="11"/>
       <c r="V17" s="22"/>
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
-      <c r="Y17" s="24"/>
+      <c r="Y17" s="28"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="22"/>
       <c r="AB17" s="11"/>
       <c r="AC17" s="11"/>
       <c r="AD17" s="11"/>
       <c r="AE17" s="11"/>
-      <c r="AF17" s="24"/>
+      <c r="AF17" s="28"/>
       <c r="AG17" s="11"/>
       <c r="AH17" s="11"/>
       <c r="AI17" s="22"/>
@@ -4716,28 +6257,28 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
-      <c r="K18" s="24"/>
+      <c r="K18" s="28"/>
       <c r="L18" s="11"/>
       <c r="M18" s="22"/>
       <c r="N18" s="11"/>
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
-      <c r="R18" s="24"/>
+      <c r="R18" s="28"/>
       <c r="S18" s="11"/>
       <c r="T18" s="22"/>
       <c r="U18" s="11"/>
       <c r="V18" s="22"/>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
-      <c r="Y18" s="24"/>
+      <c r="Y18" s="28"/>
       <c r="Z18" s="11"/>
       <c r="AA18" s="22"/>
       <c r="AB18" s="11"/>
       <c r="AC18" s="11"/>
       <c r="AD18" s="11"/>
       <c r="AE18" s="11"/>
-      <c r="AF18" s="24"/>
+      <c r="AF18" s="28"/>
       <c r="AG18" s="11"/>
       <c r="AH18" s="11"/>
       <c r="AI18" s="22"/>
@@ -4787,28 +6328,28 @@
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
-      <c r="K19" s="24"/>
+      <c r="K19" s="28"/>
       <c r="L19" s="11"/>
       <c r="M19" s="22"/>
       <c r="N19" s="11"/>
       <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
-      <c r="R19" s="24"/>
+      <c r="R19" s="28"/>
       <c r="S19" s="11"/>
       <c r="T19" s="22"/>
       <c r="U19" s="11"/>
       <c r="V19" s="22"/>
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
-      <c r="Y19" s="24"/>
+      <c r="Y19" s="28"/>
       <c r="Z19" s="11"/>
       <c r="AA19" s="22"/>
       <c r="AB19" s="11"/>
       <c r="AC19" s="11"/>
       <c r="AD19" s="11"/>
       <c r="AE19" s="11"/>
-      <c r="AF19" s="24"/>
+      <c r="AF19" s="28"/>
       <c r="AG19" s="11"/>
       <c r="AH19" s="11"/>
       <c r="AI19" s="22"/>
@@ -4858,28 +6399,28 @@
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
-      <c r="K20" s="24"/>
+      <c r="K20" s="28"/>
       <c r="L20" s="11"/>
       <c r="M20" s="22"/>
       <c r="N20" s="11"/>
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
-      <c r="R20" s="24"/>
+      <c r="R20" s="28"/>
       <c r="S20" s="11"/>
       <c r="T20" s="22"/>
       <c r="U20" s="11"/>
       <c r="V20" s="22"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
-      <c r="Y20" s="24"/>
+      <c r="Y20" s="28"/>
       <c r="Z20" s="11"/>
       <c r="AA20" s="22"/>
       <c r="AB20" s="11"/>
       <c r="AC20" s="11"/>
       <c r="AD20" s="11"/>
       <c r="AE20" s="11"/>
-      <c r="AF20" s="24"/>
+      <c r="AF20" s="28"/>
       <c r="AG20" s="11"/>
       <c r="AH20" s="11"/>
       <c r="AI20" s="22"/>
@@ -4929,28 +6470,28 @@
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-      <c r="K21" s="24"/>
+      <c r="K21" s="28"/>
       <c r="L21" s="11"/>
       <c r="M21" s="22"/>
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
-      <c r="R21" s="24"/>
+      <c r="R21" s="28"/>
       <c r="S21" s="11"/>
       <c r="T21" s="22"/>
       <c r="U21" s="11"/>
       <c r="V21" s="22"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
-      <c r="Y21" s="24"/>
+      <c r="Y21" s="28"/>
       <c r="Z21" s="11"/>
       <c r="AA21" s="22"/>
       <c r="AB21" s="11"/>
       <c r="AC21" s="11"/>
       <c r="AD21" s="11"/>
       <c r="AE21" s="11"/>
-      <c r="AF21" s="24"/>
+      <c r="AF21" s="28"/>
       <c r="AG21" s="11"/>
       <c r="AH21" s="11"/>
       <c r="AI21" s="22"/>
@@ -4985,28 +6526,28 @@
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
-      <c r="K22" s="24"/>
+      <c r="K22" s="28"/>
       <c r="L22" s="11"/>
       <c r="M22" s="22"/>
       <c r="N22" s="11"/>
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="11"/>
-      <c r="R22" s="24"/>
+      <c r="R22" s="28"/>
       <c r="S22" s="11"/>
       <c r="T22" s="22"/>
       <c r="U22" s="11"/>
       <c r="V22" s="22"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
-      <c r="Y22" s="24"/>
+      <c r="Y22" s="28"/>
       <c r="Z22" s="11"/>
       <c r="AA22" s="22"/>
       <c r="AB22" s="11"/>
       <c r="AC22" s="11"/>
       <c r="AD22" s="11"/>
       <c r="AE22" s="11"/>
-      <c r="AF22" s="24"/>
+      <c r="AF22" s="28"/>
       <c r="AG22" s="11"/>
       <c r="AH22" s="11"/>
       <c r="AI22" s="22"/>
@@ -5039,28 +6580,28 @@
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
-      <c r="K23" s="24"/>
+      <c r="K23" s="28"/>
       <c r="L23" s="11"/>
       <c r="M23" s="22"/>
       <c r="N23" s="11"/>
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
-      <c r="R23" s="24"/>
+      <c r="R23" s="28"/>
       <c r="S23" s="11"/>
       <c r="T23" s="22"/>
       <c r="U23" s="11"/>
       <c r="V23" s="22"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
-      <c r="Y23" s="24"/>
+      <c r="Y23" s="28"/>
       <c r="Z23" s="11"/>
       <c r="AA23" s="22"/>
       <c r="AB23" s="11"/>
       <c r="AC23" s="11"/>
       <c r="AD23" s="11"/>
       <c r="AE23" s="11"/>
-      <c r="AF23" s="24"/>
+      <c r="AF23" s="28"/>
       <c r="AG23" s="11"/>
       <c r="AH23" s="11"/>
       <c r="AI23" s="22"/>
@@ -5093,28 +6634,28 @@
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
-      <c r="K24" s="24"/>
+      <c r="K24" s="28"/>
       <c r="L24" s="11"/>
       <c r="M24" s="22"/>
       <c r="N24" s="11"/>
       <c r="O24" s="11"/>
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
-      <c r="R24" s="24"/>
+      <c r="R24" s="28"/>
       <c r="S24" s="11"/>
       <c r="T24" s="22"/>
       <c r="U24" s="11"/>
       <c r="V24" s="22"/>
       <c r="W24" s="11"/>
       <c r="X24" s="11"/>
-      <c r="Y24" s="24"/>
+      <c r="Y24" s="28"/>
       <c r="Z24" s="11"/>
       <c r="AA24" s="22"/>
       <c r="AB24" s="11"/>
       <c r="AC24" s="11"/>
       <c r="AD24" s="11"/>
       <c r="AE24" s="11"/>
-      <c r="AF24" s="24"/>
+      <c r="AF24" s="28"/>
       <c r="AG24" s="11"/>
       <c r="AH24" s="11"/>
       <c r="AI24" s="22"/>
@@ -5147,28 +6688,28 @@
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
-      <c r="K25" s="24"/>
+      <c r="K25" s="28"/>
       <c r="L25" s="11"/>
       <c r="M25" s="22"/>
       <c r="N25" s="11"/>
       <c r="O25" s="11"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
-      <c r="R25" s="24"/>
+      <c r="R25" s="28"/>
       <c r="S25" s="11"/>
       <c r="T25" s="22"/>
       <c r="U25" s="11"/>
       <c r="V25" s="22"/>
       <c r="W25" s="11"/>
       <c r="X25" s="11"/>
-      <c r="Y25" s="24"/>
+      <c r="Y25" s="28"/>
       <c r="Z25" s="11"/>
       <c r="AA25" s="22"/>
       <c r="AB25" s="11"/>
       <c r="AC25" s="11"/>
       <c r="AD25" s="11"/>
       <c r="AE25" s="11"/>
-      <c r="AF25" s="24"/>
+      <c r="AF25" s="28"/>
       <c r="AG25" s="11"/>
       <c r="AH25" s="11"/>
       <c r="AI25" s="22"/>
@@ -5203,28 +6744,28 @@
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
-      <c r="K26" s="24"/>
+      <c r="K26" s="28"/>
       <c r="L26" s="11"/>
       <c r="M26" s="22"/>
       <c r="N26" s="11"/>
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
-      <c r="R26" s="24"/>
+      <c r="R26" s="28"/>
       <c r="S26" s="11"/>
       <c r="T26" s="22"/>
       <c r="U26" s="11"/>
       <c r="V26" s="22"/>
       <c r="W26" s="11"/>
       <c r="X26" s="11"/>
-      <c r="Y26" s="24"/>
+      <c r="Y26" s="28"/>
       <c r="Z26" s="11"/>
       <c r="AA26" s="22"/>
       <c r="AB26" s="11"/>
       <c r="AC26" s="11"/>
       <c r="AD26" s="11"/>
       <c r="AE26" s="11"/>
-      <c r="AF26" s="24"/>
+      <c r="AF26" s="28"/>
       <c r="AG26" s="11"/>
       <c r="AH26" s="11"/>
       <c r="AI26" s="22"/>
@@ -5259,28 +6800,28 @@
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
-      <c r="K27" s="24"/>
+      <c r="K27" s="28"/>
       <c r="L27" s="11"/>
       <c r="M27" s="22"/>
       <c r="N27" s="11"/>
       <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
-      <c r="R27" s="24"/>
+      <c r="R27" s="28"/>
       <c r="S27" s="11"/>
       <c r="T27" s="22"/>
       <c r="U27" s="11"/>
       <c r="V27" s="22"/>
       <c r="W27" s="11"/>
       <c r="X27" s="11"/>
-      <c r="Y27" s="24"/>
+      <c r="Y27" s="28"/>
       <c r="Z27" s="11"/>
       <c r="AA27" s="22"/>
       <c r="AB27" s="11"/>
       <c r="AC27" s="11"/>
       <c r="AD27" s="11"/>
       <c r="AE27" s="11"/>
-      <c r="AF27" s="24"/>
+      <c r="AF27" s="28"/>
       <c r="AG27" s="11"/>
       <c r="AH27" s="11"/>
       <c r="AI27" s="22"/>
@@ -5313,28 +6854,28 @@
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
-      <c r="K28" s="24"/>
+      <c r="K28" s="28"/>
       <c r="L28" s="11"/>
       <c r="M28" s="22"/>
       <c r="N28" s="11"/>
       <c r="O28" s="11"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
-      <c r="R28" s="24"/>
+      <c r="R28" s="28"/>
       <c r="S28" s="11"/>
       <c r="T28" s="22"/>
       <c r="U28" s="11"/>
       <c r="V28" s="22"/>
       <c r="W28" s="11"/>
       <c r="X28" s="11"/>
-      <c r="Y28" s="24"/>
+      <c r="Y28" s="28"/>
       <c r="Z28" s="11"/>
       <c r="AA28" s="22"/>
       <c r="AB28" s="11"/>
       <c r="AC28" s="11"/>
       <c r="AD28" s="11"/>
       <c r="AE28" s="11"/>
-      <c r="AF28" s="24"/>
+      <c r="AF28" s="28"/>
       <c r="AG28" s="11"/>
       <c r="AH28" s="11"/>
       <c r="AI28" s="22"/>
@@ -5367,28 +6908,28 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
-      <c r="K29" s="24"/>
+      <c r="K29" s="28"/>
       <c r="L29" s="11"/>
       <c r="M29" s="22"/>
       <c r="N29" s="11"/>
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
-      <c r="R29" s="24"/>
+      <c r="R29" s="28"/>
       <c r="S29" s="11"/>
       <c r="T29" s="22"/>
       <c r="U29" s="11"/>
       <c r="V29" s="22"/>
       <c r="W29" s="11"/>
       <c r="X29" s="11"/>
-      <c r="Y29" s="24"/>
+      <c r="Y29" s="28"/>
       <c r="Z29" s="11"/>
       <c r="AA29" s="22"/>
       <c r="AB29" s="11"/>
       <c r="AC29" s="11"/>
       <c r="AD29" s="11"/>
       <c r="AE29" s="11"/>
-      <c r="AF29" s="24"/>
+      <c r="AF29" s="28"/>
       <c r="AG29" s="11"/>
       <c r="AH29" s="11"/>
       <c r="AI29" s="22"/>
@@ -5421,28 +6962,28 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
-      <c r="K30" s="25"/>
+      <c r="K30" s="29"/>
       <c r="L30" s="11"/>
       <c r="M30" s="22"/>
       <c r="N30" s="11"/>
       <c r="O30" s="11"/>
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
-      <c r="R30" s="25"/>
+      <c r="R30" s="29"/>
       <c r="S30" s="11"/>
       <c r="T30" s="22"/>
       <c r="U30" s="11"/>
       <c r="V30" s="22"/>
       <c r="W30" s="11"/>
       <c r="X30" s="11"/>
-      <c r="Y30" s="25"/>
+      <c r="Y30" s="29"/>
       <c r="Z30" s="11"/>
       <c r="AA30" s="22"/>
       <c r="AB30" s="11"/>
       <c r="AC30" s="11"/>
       <c r="AD30" s="11"/>
       <c r="AE30" s="11"/>
-      <c r="AF30" s="25"/>
+      <c r="AF30" s="29"/>
       <c r="AG30" s="11"/>
       <c r="AH30" s="11"/>
       <c r="AI30" s="22"/>
@@ -5458,6 +6999,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="AM8:AP8"/>
+    <mergeCell ref="AM16:AP16"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="K5:K30"/>
+    <mergeCell ref="R5:R30"/>
+    <mergeCell ref="Y5:Y30"/>
+    <mergeCell ref="AF5:AF30"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="AM3:AN3"/>
@@ -5466,14 +7015,6 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A1:AJ1"/>
-    <mergeCell ref="K5:K30"/>
-    <mergeCell ref="R5:R30"/>
-    <mergeCell ref="Y5:Y30"/>
-    <mergeCell ref="AF5:AF30"/>
-    <mergeCell ref="AM8:AP8"/>
-    <mergeCell ref="AM16:AP16"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B30">
     <cfRule type="duplicateValues" dxfId="12" priority="25"/>

--- a/Sindhi Muslim/Student Attendance/Class 3/Class 3 - Monthly Attendance - October-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/Class 3/Class 3 - Monthly Attendance - October-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\Class 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46D130F-34C3-4760-9A71-398BD584DBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45E3794-4859-4D12-8E68-074036B06688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="135">
   <si>
     <t>S.No</t>
   </si>
@@ -431,6 +431,15 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>Muhammad Essa</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PTM - PTM - PTM - PTM - PTM - PTM - PTM</t>
   </si>
 </sst>
 </file>
@@ -662,7 +671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -709,19 +718,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -739,23 +742,35 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <alignment horizontal="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -909,13 +924,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -949,6 +957,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1238,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3AEC60-7EB8-45C3-AF72-C11F7CE845DC}">
-  <dimension ref="A1:AP33"/>
+  <dimension ref="A1:AP34"/>
   <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1282,99 +1297,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="24"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="24"/>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
+      <c r="AH1" s="24"/>
+      <c r="AI1" s="24"/>
+      <c r="AJ1" s="24"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="28" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1501,25 +1516,25 @@
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="23" t="s">
+      <c r="AK3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="23" t="s">
+      <c r="AL3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="24" t="s">
+      <c r="AM3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="25"/>
+      <c r="AN3" s="32"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="21">
         <v>45566</v>
       </c>
@@ -1613,8 +1628,8 @@
       <c r="AJ4" s="21">
         <v>45596</v>
       </c>
-      <c r="AK4" s="23"/>
-      <c r="AL4" s="23"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="30"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1640,22 +1655,22 @@
       <c r="E5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I5" s="34" t="s">
+      <c r="F5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="22" t="s">
         <v>128</v>
       </c>
       <c r="J5" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="36" t="s">
         <v>126</v>
       </c>
       <c r="L5" s="11" t="s">
@@ -1676,7 +1691,7 @@
       <c r="Q5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R5" s="27" t="s">
+      <c r="R5" s="36" t="s">
         <v>126</v>
       </c>
       <c r="S5" s="11" t="s">
@@ -1697,7 +1712,7 @@
       <c r="X5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y5" s="27" t="s">
+      <c r="Y5" s="36" t="s">
         <v>126</v>
       </c>
       <c r="Z5" s="11" t="s">
@@ -1718,7 +1733,7 @@
       <c r="AE5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF5" s="27" t="s">
+      <c r="AF5" s="36" t="s">
         <v>126</v>
       </c>
       <c r="AG5" s="11" t="s">
@@ -1734,11 +1749,11 @@
         <v>128</v>
       </c>
       <c r="AK5" s="5">
-        <f t="shared" ref="AK5:AK33" si="2">COUNTIF(F5:AJ5,"P")</f>
+        <f t="shared" ref="AK5:AK34" si="2">COUNTIF(F5:AJ5,"P")</f>
         <v>26</v>
       </c>
       <c r="AL5" s="5">
-        <f t="shared" ref="AL5:AL33" si="3">COUNTIF(F5:AJ5,"A")</f>
+        <f t="shared" ref="AL5:AL34" si="3">COUNTIF(F5:AJ5,"A")</f>
         <v>0</v>
       </c>
       <c r="AM5" s="5" t="s">
@@ -1766,20 +1781,20 @@
       <c r="E6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="28"/>
+      <c r="F6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="35"/>
+      <c r="K6" s="36"/>
       <c r="L6" s="11" t="s">
         <v>128</v>
       </c>
@@ -1798,7 +1813,7 @@
       <c r="Q6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R6" s="28"/>
+      <c r="R6" s="36"/>
       <c r="S6" s="11" t="s">
         <v>128</v>
       </c>
@@ -1817,7 +1832,7 @@
       <c r="X6" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="Y6" s="28"/>
+      <c r="Y6" s="36"/>
       <c r="Z6" s="11" t="s">
         <v>128</v>
       </c>
@@ -1836,7 +1851,7 @@
       <c r="AE6" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF6" s="28"/>
+      <c r="AF6" s="36"/>
       <c r="AG6" s="11" t="s">
         <v>128</v>
       </c>
@@ -1882,20 +1897,20 @@
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="28"/>
+      <c r="F7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="36"/>
       <c r="L7" s="11" t="s">
         <v>128</v>
       </c>
@@ -1914,7 +1929,7 @@
       <c r="Q7" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R7" s="28"/>
+      <c r="R7" s="36"/>
       <c r="S7" s="11" t="s">
         <v>128</v>
       </c>
@@ -1933,7 +1948,7 @@
       <c r="X7" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y7" s="28"/>
+      <c r="Y7" s="36"/>
       <c r="Z7" s="11" t="s">
         <v>128</v>
       </c>
@@ -1952,7 +1967,7 @@
       <c r="AE7" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF7" s="28"/>
+      <c r="AF7" s="36"/>
       <c r="AG7" s="11" t="s">
         <v>128</v>
       </c>
@@ -1994,20 +2009,20 @@
       <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J8" s="36"/>
-      <c r="K8" s="28"/>
+      <c r="F8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" s="35"/>
+      <c r="K8" s="36"/>
       <c r="L8" s="11" t="s">
         <v>128</v>
       </c>
@@ -2026,7 +2041,7 @@
       <c r="Q8" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R8" s="28"/>
+      <c r="R8" s="36"/>
       <c r="S8" s="11" t="s">
         <v>128</v>
       </c>
@@ -2045,7 +2060,7 @@
       <c r="X8" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y8" s="28"/>
+      <c r="Y8" s="36"/>
       <c r="Z8" s="11" t="s">
         <v>128</v>
       </c>
@@ -2064,7 +2079,7 @@
       <c r="AE8" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF8" s="28"/>
+      <c r="AF8" s="36"/>
       <c r="AG8" s="11" t="s">
         <v>128</v>
       </c>
@@ -2085,12 +2100,12 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="AM8" s="24" t="s">
+      <c r="AM8" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="AN8" s="25"/>
-      <c r="AO8" s="25"/>
-      <c r="AP8" s="26"/>
+      <c r="AN8" s="32"/>
+      <c r="AO8" s="32"/>
+      <c r="AP8" s="33"/>
     </row>
     <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
@@ -2108,20 +2123,20 @@
       <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J9" s="36"/>
-      <c r="K9" s="28"/>
+      <c r="F9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="35"/>
+      <c r="K9" s="36"/>
       <c r="L9" s="11" t="s">
         <v>128</v>
       </c>
@@ -2140,7 +2155,7 @@
       <c r="Q9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R9" s="28"/>
+      <c r="R9" s="36"/>
       <c r="S9" s="11" t="s">
         <v>128</v>
       </c>
@@ -2159,7 +2174,7 @@
       <c r="X9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y9" s="28"/>
+      <c r="Y9" s="36"/>
       <c r="Z9" s="11" t="s">
         <v>128</v>
       </c>
@@ -2178,7 +2193,7 @@
       <c r="AE9" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF9" s="28"/>
+      <c r="AF9" s="36"/>
       <c r="AG9" s="11" t="s">
         <v>128</v>
       </c>
@@ -2228,20 +2243,20 @@
       <c r="E10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="28"/>
+      <c r="F10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J10" s="35"/>
+      <c r="K10" s="36"/>
       <c r="L10" s="11" t="s">
         <v>128</v>
       </c>
@@ -2260,7 +2275,7 @@
       <c r="Q10" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R10" s="28"/>
+      <c r="R10" s="36"/>
       <c r="S10" s="11" t="s">
         <v>128</v>
       </c>
@@ -2279,7 +2294,7 @@
       <c r="X10" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y10" s="28"/>
+      <c r="Y10" s="36"/>
       <c r="Z10" s="11" t="s">
         <v>128</v>
       </c>
@@ -2298,7 +2313,7 @@
       <c r="AE10" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF10" s="28"/>
+      <c r="AF10" s="36"/>
       <c r="AG10" s="11" t="s">
         <v>128</v>
       </c>
@@ -2351,20 +2366,20 @@
       <c r="E11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I11" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J11" s="36"/>
-      <c r="K11" s="28"/>
+      <c r="F11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="35"/>
+      <c r="K11" s="36"/>
       <c r="L11" s="11" t="s">
         <v>128</v>
       </c>
@@ -2383,7 +2398,7 @@
       <c r="Q11" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R11" s="28"/>
+      <c r="R11" s="36"/>
       <c r="S11" s="11" t="s">
         <v>128</v>
       </c>
@@ -2402,7 +2417,7 @@
       <c r="X11" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="Y11" s="28"/>
+      <c r="Y11" s="36"/>
       <c r="Z11" s="11" t="s">
         <v>128</v>
       </c>
@@ -2421,7 +2436,7 @@
       <c r="AE11" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF11" s="28"/>
+      <c r="AF11" s="36"/>
       <c r="AG11" s="11" t="s">
         <v>128</v>
       </c>
@@ -2474,20 +2489,20 @@
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="28"/>
+      <c r="F12" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36"/>
       <c r="L12" s="11" t="s">
         <v>130</v>
       </c>
@@ -2506,7 +2521,7 @@
       <c r="Q12" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R12" s="28"/>
+      <c r="R12" s="36"/>
       <c r="S12" s="11" t="s">
         <v>130</v>
       </c>
@@ -2525,7 +2540,7 @@
       <c r="X12" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="Y12" s="28"/>
+      <c r="Y12" s="36"/>
       <c r="Z12" s="11" t="s">
         <v>130</v>
       </c>
@@ -2544,7 +2559,7 @@
       <c r="AE12" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF12" s="28"/>
+      <c r="AF12" s="36"/>
       <c r="AG12" s="11" t="s">
         <v>130</v>
       </c>
@@ -2597,20 +2612,20 @@
       <c r="E13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="28"/>
+      <c r="F13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="35"/>
+      <c r="K13" s="36"/>
       <c r="L13" s="11" t="s">
         <v>130</v>
       </c>
@@ -2629,7 +2644,7 @@
       <c r="Q13" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R13" s="28"/>
+      <c r="R13" s="36"/>
       <c r="S13" s="11" t="s">
         <v>128</v>
       </c>
@@ -2648,7 +2663,7 @@
       <c r="X13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y13" s="28"/>
+      <c r="Y13" s="36"/>
       <c r="Z13" s="11" t="s">
         <v>128</v>
       </c>
@@ -2667,7 +2682,7 @@
       <c r="AE13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF13" s="28"/>
+      <c r="AF13" s="36"/>
       <c r="AG13" s="11" t="s">
         <v>130</v>
       </c>
@@ -2709,20 +2724,20 @@
       <c r="E14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J14" s="36"/>
-      <c r="K14" s="28"/>
+      <c r="F14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="35"/>
+      <c r="K14" s="36"/>
       <c r="L14" s="11" t="s">
         <v>130</v>
       </c>
@@ -2741,7 +2756,7 @@
       <c r="Q14" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R14" s="28"/>
+      <c r="R14" s="36"/>
       <c r="S14" s="11" t="s">
         <v>128</v>
       </c>
@@ -2760,7 +2775,7 @@
       <c r="X14" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y14" s="28"/>
+      <c r="Y14" s="36"/>
       <c r="Z14" s="11" t="s">
         <v>128</v>
       </c>
@@ -2779,7 +2794,7 @@
       <c r="AE14" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF14" s="28"/>
+      <c r="AF14" s="36"/>
       <c r="AG14" s="11" t="s">
         <v>130</v>
       </c>
@@ -2821,20 +2836,20 @@
       <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="28"/>
+      <c r="F15" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J15" s="35"/>
+      <c r="K15" s="36"/>
       <c r="L15" s="11" t="s">
         <v>128</v>
       </c>
@@ -2853,7 +2868,7 @@
       <c r="Q15" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R15" s="28"/>
+      <c r="R15" s="36"/>
       <c r="S15" s="11" t="s">
         <v>128</v>
       </c>
@@ -2872,7 +2887,7 @@
       <c r="X15" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="Y15" s="28"/>
+      <c r="Y15" s="36"/>
       <c r="Z15" s="11" t="s">
         <v>128</v>
       </c>
@@ -2891,7 +2906,7 @@
       <c r="AE15" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF15" s="28"/>
+      <c r="AF15" s="36"/>
       <c r="AG15" s="11" t="s">
         <v>128</v>
       </c>
@@ -2933,20 +2948,20 @@
       <c r="E16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G16" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I16" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J16" s="36"/>
-      <c r="K16" s="28"/>
+      <c r="F16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="35"/>
+      <c r="K16" s="36"/>
       <c r="L16" s="11" t="s">
         <v>128</v>
       </c>
@@ -2965,7 +2980,7 @@
       <c r="Q16" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R16" s="28"/>
+      <c r="R16" s="36"/>
       <c r="S16" s="11" t="s">
         <v>128</v>
       </c>
@@ -2984,7 +2999,7 @@
       <c r="X16" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y16" s="28"/>
+      <c r="Y16" s="36"/>
       <c r="Z16" s="11" t="s">
         <v>128</v>
       </c>
@@ -3003,7 +3018,7 @@
       <c r="AE16" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF16" s="28"/>
+      <c r="AF16" s="36"/>
       <c r="AG16" s="11" t="s">
         <v>128</v>
       </c>
@@ -3024,12 +3039,12 @@
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AM16" s="24" t="s">
+      <c r="AM16" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="25"/>
-      <c r="AO16" s="25"/>
-      <c r="AP16" s="26"/>
+      <c r="AN16" s="32"/>
+      <c r="AO16" s="32"/>
+      <c r="AP16" s="33"/>
     </row>
     <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
@@ -3047,20 +3062,20 @@
       <c r="E17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I17" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="28"/>
+      <c r="F17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="35"/>
+      <c r="K17" s="36"/>
       <c r="L17" s="11" t="s">
         <v>128</v>
       </c>
@@ -3079,7 +3094,7 @@
       <c r="Q17" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R17" s="28"/>
+      <c r="R17" s="36"/>
       <c r="S17" s="11" t="s">
         <v>128</v>
       </c>
@@ -3098,7 +3113,7 @@
       <c r="X17" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y17" s="28"/>
+      <c r="Y17" s="36"/>
       <c r="Z17" s="11" t="s">
         <v>128</v>
       </c>
@@ -3117,7 +3132,7 @@
       <c r="AE17" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF17" s="28"/>
+      <c r="AF17" s="36"/>
       <c r="AG17" s="11" t="s">
         <v>130</v>
       </c>
@@ -3167,20 +3182,20 @@
       <c r="E18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G18" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H18" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I18" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J18" s="36"/>
-      <c r="K18" s="28"/>
+      <c r="F18" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J18" s="35"/>
+      <c r="K18" s="36"/>
       <c r="L18" s="11" t="s">
         <v>128</v>
       </c>
@@ -3199,7 +3214,7 @@
       <c r="Q18" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R18" s="28"/>
+      <c r="R18" s="36"/>
       <c r="S18" s="11" t="s">
         <v>128</v>
       </c>
@@ -3218,7 +3233,7 @@
       <c r="X18" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y18" s="28"/>
+      <c r="Y18" s="36"/>
       <c r="Z18" s="11" t="s">
         <v>128</v>
       </c>
@@ -3237,7 +3252,7 @@
       <c r="AE18" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF18" s="28"/>
+      <c r="AF18" s="36"/>
       <c r="AG18" s="11" t="s">
         <v>128</v>
       </c>
@@ -3290,20 +3305,20 @@
       <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G19" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J19" s="36"/>
-      <c r="K19" s="28"/>
+      <c r="F19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J19" s="35"/>
+      <c r="K19" s="36"/>
       <c r="L19" s="11" t="s">
         <v>128</v>
       </c>
@@ -3322,7 +3337,7 @@
       <c r="Q19" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R19" s="28"/>
+      <c r="R19" s="36"/>
       <c r="S19" s="11" t="s">
         <v>128</v>
       </c>
@@ -3341,7 +3356,7 @@
       <c r="X19" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y19" s="28"/>
+      <c r="Y19" s="36"/>
       <c r="Z19" s="11" t="s">
         <v>131</v>
       </c>
@@ -3360,7 +3375,7 @@
       <c r="AE19" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF19" s="28"/>
+      <c r="AF19" s="36"/>
       <c r="AG19" s="11" t="s">
         <v>128</v>
       </c>
@@ -3413,20 +3428,20 @@
       <c r="E20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I20" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J20" s="36"/>
-      <c r="K20" s="28"/>
+      <c r="F20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="35"/>
+      <c r="K20" s="36"/>
       <c r="L20" s="11" t="s">
         <v>130</v>
       </c>
@@ -3445,7 +3460,7 @@
       <c r="Q20" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R20" s="28"/>
+      <c r="R20" s="36"/>
       <c r="S20" s="11" t="s">
         <v>128</v>
       </c>
@@ -3464,7 +3479,7 @@
       <c r="X20" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y20" s="28"/>
+      <c r="Y20" s="36"/>
       <c r="Z20" s="11" t="s">
         <v>128</v>
       </c>
@@ -3483,7 +3498,7 @@
       <c r="AE20" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="AF20" s="28"/>
+      <c r="AF20" s="36"/>
       <c r="AG20" s="11" t="s">
         <v>128</v>
       </c>
@@ -3536,20 +3551,20 @@
       <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="28"/>
+      <c r="F21" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="35"/>
+      <c r="K21" s="36"/>
       <c r="L21" s="11" t="s">
         <v>130</v>
       </c>
@@ -3568,7 +3583,7 @@
       <c r="Q21" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R21" s="28"/>
+      <c r="R21" s="36"/>
       <c r="S21" s="11" t="s">
         <v>130</v>
       </c>
@@ -3587,7 +3602,7 @@
       <c r="X21" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="Y21" s="28"/>
+      <c r="Y21" s="36"/>
       <c r="Z21" s="11" t="s">
         <v>130</v>
       </c>
@@ -3606,7 +3621,7 @@
       <c r="AE21" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF21" s="28"/>
+      <c r="AF21" s="36"/>
       <c r="AG21" s="11" t="s">
         <v>130</v>
       </c>
@@ -3644,20 +3659,20 @@
       <c r="E22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I22" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J22" s="36"/>
-      <c r="K22" s="28"/>
+      <c r="F22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J22" s="35"/>
+      <c r="K22" s="36"/>
       <c r="L22" s="11" t="s">
         <v>128</v>
       </c>
@@ -3676,7 +3691,7 @@
       <c r="Q22" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R22" s="28"/>
+      <c r="R22" s="36"/>
       <c r="S22" s="11" t="s">
         <v>128</v>
       </c>
@@ -3695,7 +3710,7 @@
       <c r="X22" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y22" s="28"/>
+      <c r="Y22" s="36"/>
       <c r="Z22" s="11" t="s">
         <v>128</v>
       </c>
@@ -3714,7 +3729,7 @@
       <c r="AE22" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF22" s="28"/>
+      <c r="AF22" s="36"/>
       <c r="AG22" s="11" t="s">
         <v>128</v>
       </c>
@@ -3752,20 +3767,20 @@
       <c r="E23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H23" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I23" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J23" s="36"/>
-      <c r="K23" s="28"/>
+      <c r="F23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="35"/>
+      <c r="K23" s="36"/>
       <c r="L23" s="11" t="s">
         <v>128</v>
       </c>
@@ -3784,7 +3799,7 @@
       <c r="Q23" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R23" s="28"/>
+      <c r="R23" s="36"/>
       <c r="S23" s="11" t="s">
         <v>130</v>
       </c>
@@ -3803,7 +3818,7 @@
       <c r="X23" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="Y23" s="28"/>
+      <c r="Y23" s="36"/>
       <c r="Z23" s="11" t="s">
         <v>128</v>
       </c>
@@ -3822,7 +3837,7 @@
       <c r="AE23" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF23" s="28"/>
+      <c r="AF23" s="36"/>
       <c r="AG23" s="11" t="s">
         <v>128</v>
       </c>
@@ -3860,20 +3875,20 @@
       <c r="E24" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G24" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H24" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I24" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J24" s="36"/>
-      <c r="K24" s="28"/>
+      <c r="F24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="35"/>
+      <c r="K24" s="36"/>
       <c r="L24" s="11" t="s">
         <v>128</v>
       </c>
@@ -3892,7 +3907,7 @@
       <c r="Q24" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R24" s="28"/>
+      <c r="R24" s="36"/>
       <c r="S24" s="11" t="s">
         <v>128</v>
       </c>
@@ -3911,7 +3926,7 @@
       <c r="X24" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y24" s="28"/>
+      <c r="Y24" s="36"/>
       <c r="Z24" s="11" t="s">
         <v>128</v>
       </c>
@@ -3930,7 +3945,7 @@
       <c r="AE24" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF24" s="28"/>
+      <c r="AF24" s="36"/>
       <c r="AG24" s="11" t="s">
         <v>128</v>
       </c>
@@ -3968,20 +3983,20 @@
       <c r="E25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H25" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I25" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J25" s="36"/>
-      <c r="K25" s="28"/>
+      <c r="F25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="35"/>
+      <c r="K25" s="36"/>
       <c r="L25" s="11" t="s">
         <v>128</v>
       </c>
@@ -4000,7 +4015,7 @@
       <c r="Q25" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R25" s="28"/>
+      <c r="R25" s="36"/>
       <c r="S25" s="11" t="s">
         <v>128</v>
       </c>
@@ -4019,7 +4034,7 @@
       <c r="X25" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y25" s="28"/>
+      <c r="Y25" s="36"/>
       <c r="Z25" s="11" t="s">
         <v>131</v>
       </c>
@@ -4038,7 +4053,7 @@
       <c r="AE25" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="AF25" s="28"/>
+      <c r="AF25" s="36"/>
       <c r="AG25" s="11" t="s">
         <v>130</v>
       </c>
@@ -4076,20 +4091,20 @@
       <c r="E26" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I26" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J26" s="36"/>
-      <c r="K26" s="28"/>
+      <c r="F26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J26" s="35"/>
+      <c r="K26" s="36"/>
       <c r="L26" s="11" t="s">
         <v>128</v>
       </c>
@@ -4108,7 +4123,7 @@
       <c r="Q26" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R26" s="28"/>
+      <c r="R26" s="36"/>
       <c r="S26" s="11" t="s">
         <v>128</v>
       </c>
@@ -4127,7 +4142,7 @@
       <c r="X26" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y26" s="28"/>
+      <c r="Y26" s="36"/>
       <c r="Z26" s="11" t="s">
         <v>128</v>
       </c>
@@ -4146,7 +4161,7 @@
       <c r="AE26" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF26" s="28"/>
+      <c r="AF26" s="36"/>
       <c r="AG26" s="11" t="s">
         <v>128</v>
       </c>
@@ -4184,20 +4199,20 @@
       <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H27" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J27" s="36"/>
-      <c r="K27" s="28"/>
+      <c r="F27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="35"/>
+      <c r="K27" s="36"/>
       <c r="L27" s="11" t="s">
         <v>128</v>
       </c>
@@ -4216,7 +4231,7 @@
       <c r="Q27" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R27" s="28"/>
+      <c r="R27" s="36"/>
       <c r="S27" s="11" t="s">
         <v>128</v>
       </c>
@@ -4235,7 +4250,7 @@
       <c r="X27" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y27" s="28"/>
+      <c r="Y27" s="36"/>
       <c r="Z27" s="11" t="s">
         <v>128</v>
       </c>
@@ -4254,7 +4269,7 @@
       <c r="AE27" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF27" s="28"/>
+      <c r="AF27" s="36"/>
       <c r="AG27" s="11" t="s">
         <v>128</v>
       </c>
@@ -4292,20 +4307,20 @@
       <c r="E28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H28" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I28" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J28" s="36"/>
-      <c r="K28" s="28"/>
+      <c r="F28" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J28" s="35"/>
+      <c r="K28" s="36"/>
       <c r="L28" s="11" t="s">
         <v>130</v>
       </c>
@@ -4324,7 +4339,7 @@
       <c r="Q28" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R28" s="28"/>
+      <c r="R28" s="36"/>
       <c r="S28" s="11" t="s">
         <v>128</v>
       </c>
@@ -4343,7 +4358,7 @@
       <c r="X28" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="Y28" s="28"/>
+      <c r="Y28" s="36"/>
       <c r="Z28" s="11" t="s">
         <v>128</v>
       </c>
@@ -4362,7 +4377,7 @@
       <c r="AE28" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF28" s="28"/>
+      <c r="AF28" s="36"/>
       <c r="AG28" s="11" t="s">
         <v>128</v>
       </c>
@@ -4400,20 +4415,20 @@
       <c r="E29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I29" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J29" s="36"/>
-      <c r="K29" s="28"/>
+      <c r="F29" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J29" s="35"/>
+      <c r="K29" s="36"/>
       <c r="L29" s="11" t="s">
         <v>128</v>
       </c>
@@ -4432,7 +4447,7 @@
       <c r="Q29" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="R29" s="28"/>
+      <c r="R29" s="36"/>
       <c r="S29" s="11" t="s">
         <v>128</v>
       </c>
@@ -4451,7 +4466,7 @@
       <c r="X29" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="Y29" s="28"/>
+      <c r="Y29" s="36"/>
       <c r="Z29" s="11" t="s">
         <v>128</v>
       </c>
@@ -4470,7 +4485,7 @@
       <c r="AE29" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF29" s="28"/>
+      <c r="AF29" s="36"/>
       <c r="AG29" s="11" t="s">
         <v>128</v>
       </c>
@@ -4508,20 +4523,20 @@
       <c r="E30" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I30" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J30" s="36"/>
-      <c r="K30" s="28"/>
+      <c r="F30" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J30" s="35"/>
+      <c r="K30" s="36"/>
       <c r="L30" s="11" t="s">
         <v>128</v>
       </c>
@@ -4540,7 +4555,7 @@
       <c r="Q30" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R30" s="28"/>
+      <c r="R30" s="36"/>
       <c r="S30" s="11" t="s">
         <v>128</v>
       </c>
@@ -4559,7 +4574,7 @@
       <c r="X30" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y30" s="28"/>
+      <c r="Y30" s="36"/>
       <c r="Z30" s="11" t="s">
         <v>128</v>
       </c>
@@ -4578,7 +4593,7 @@
       <c r="AE30" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="AF30" s="28"/>
+      <c r="AF30" s="36"/>
       <c r="AG30" s="11" t="s">
         <v>128</v>
       </c>
@@ -4614,20 +4629,20 @@
       <c r="E31" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G31" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="H31" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I31" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J31" s="36"/>
-      <c r="K31" s="28"/>
+      <c r="F31" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J31" s="35"/>
+      <c r="K31" s="36"/>
       <c r="L31" s="11" t="s">
         <v>128</v>
       </c>
@@ -4646,7 +4661,7 @@
       <c r="Q31" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R31" s="28"/>
+      <c r="R31" s="36"/>
       <c r="S31" s="11" t="s">
         <v>128</v>
       </c>
@@ -4665,7 +4680,7 @@
       <c r="X31" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y31" s="28"/>
+      <c r="Y31" s="36"/>
       <c r="Z31" s="11" t="s">
         <v>128</v>
       </c>
@@ -4684,7 +4699,7 @@
       <c r="AE31" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF31" s="28"/>
+      <c r="AF31" s="36"/>
       <c r="AG31" s="11" t="s">
         <v>128</v>
       </c>
@@ -4720,20 +4735,20 @@
       <c r="E32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H32" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I32" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="J32" s="36"/>
-      <c r="K32" s="28"/>
+      <c r="F32" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J32" s="35"/>
+      <c r="K32" s="36"/>
       <c r="L32" s="11" t="s">
         <v>128</v>
       </c>
@@ -4752,7 +4767,7 @@
       <c r="Q32" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R32" s="28"/>
+      <c r="R32" s="36"/>
       <c r="S32" s="11" t="s">
         <v>128</v>
       </c>
@@ -4771,7 +4786,7 @@
       <c r="X32" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y32" s="28"/>
+      <c r="Y32" s="36"/>
       <c r="Z32" s="11" t="s">
         <v>128</v>
       </c>
@@ -4790,7 +4805,7 @@
       <c r="AE32" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF32" s="28"/>
+      <c r="AF32" s="36"/>
       <c r="AG32" s="11" t="s">
         <v>128</v>
       </c>
@@ -4826,20 +4841,20 @@
       <c r="E33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G33" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="H33" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I33" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="J33" s="37"/>
-      <c r="K33" s="29"/>
+      <c r="F33" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J33" s="35"/>
+      <c r="K33" s="36"/>
       <c r="L33" s="11" t="s">
         <v>128</v>
       </c>
@@ -4858,7 +4873,7 @@
       <c r="Q33" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R33" s="29"/>
+      <c r="R33" s="36"/>
       <c r="S33" s="11" t="s">
         <v>128</v>
       </c>
@@ -4877,7 +4892,7 @@
       <c r="X33" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="Y33" s="29"/>
+      <c r="Y33" s="36"/>
       <c r="Z33" s="11" t="s">
         <v>128</v>
       </c>
@@ -4896,7 +4911,7 @@
       <c r="AE33" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="AF33" s="29"/>
+      <c r="AF33" s="36"/>
       <c r="AG33" s="11" t="s">
         <v>128</v>
       </c>
@@ -4918,51 +4933,155 @@
         <v>2</v>
       </c>
     </row>
+    <row r="34" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A34" s="12">
+        <v>30</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="J34" s="35"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="N34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R34" s="36"/>
+      <c r="S34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V34" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y34" s="36"/>
+      <c r="Z34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF34" s="36"/>
+      <c r="AG34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK34" s="5">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="AL34" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AF5:AF34"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM3:AN3"/>
+    <mergeCell ref="AM8:AP8"/>
+    <mergeCell ref="AM16:AP16"/>
     <mergeCell ref="A2:AJ2"/>
     <mergeCell ref="A1:AJ1"/>
-    <mergeCell ref="J5:J33"/>
-    <mergeCell ref="Y5:Y33"/>
-    <mergeCell ref="AF5:AF33"/>
-    <mergeCell ref="K5:K33"/>
-    <mergeCell ref="R5:R33"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AN3"/>
-    <mergeCell ref="AM8:AP8"/>
-    <mergeCell ref="AM16:AP16"/>
+    <mergeCell ref="J5:J34"/>
+    <mergeCell ref="K5:K34"/>
+    <mergeCell ref="R5:R34"/>
+    <mergeCell ref="Y5:Y34"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B33">
+  <conditionalFormatting sqref="B5:B34">
     <cfRule type="duplicateValues" dxfId="24" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:I33 L6:Q33 S6:X33 Z6:AE33 F4:AJ5 AG6:AJ33">
-    <cfRule type="expression" dxfId="23" priority="15">
+  <conditionalFormatting sqref="F3:AJ5 AM4:AN4 F6:I34 L6:Q34 S6:X34 Z6:AE34 AG6:AJ34">
+    <cfRule type="expression" dxfId="23" priority="16">
+      <formula>F$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:AJ5 F6:I34 L6:Q34 S6:X34 Z6:AE34 AG6:AJ34">
+    <cfRule type="expression" dxfId="22" priority="15">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:I33 L6:Q33 S6:X33 Z6:AE33 F5:AJ5 AG6:AJ33">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+  <conditionalFormatting sqref="F5:AJ5 F6:I34 L6:Q34 S6:X34 Z6:AE34 AG6:AJ34">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM4:AN4 F6:I33 L6:Q33 S6:X33 Z6:AE33 F3:AJ5 AG6:AJ33">
-    <cfRule type="expression" dxfId="19" priority="16">
-      <formula>F$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK3:AL3 AK5:AL33">
+  <conditionalFormatting sqref="AK3:AL3 AK5:AL34">
     <cfRule type="expression" dxfId="18" priority="17">
       <formula>#REF!="Sun"</formula>
     </cfRule>
@@ -5043,99 +5162,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="24"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="24"/>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
+      <c r="AH1" s="24"/>
+      <c r="AI1" s="24"/>
+      <c r="AJ1" s="24"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="28" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -5262,25 +5381,25 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="23" t="s">
+      <c r="AK3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="23" t="s">
+      <c r="AL3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="24" t="s">
+      <c r="AM3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="25"/>
+      <c r="AN3" s="32"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="21">
         <v>45566</v>
       </c>
@@ -5374,8 +5493,8 @@
       <c r="AJ4" s="21">
         <v>45596</v>
       </c>
-      <c r="AK4" s="23"/>
-      <c r="AL4" s="23"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="30"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -5401,52 +5520,106 @@
       <c r="E5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="27" t="s">
+      <c r="F5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="27" t="s">
+      <c r="L5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R5" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="27" t="s">
+      <c r="S5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y5" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="27" t="s">
+      <c r="Z5" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF5" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="22"/>
-      <c r="AJ5" s="11"/>
+      <c r="AG5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ5" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK30" si="1">COUNTIF(F5:AJ5,"P")</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL5" s="5">
         <f t="shared" ref="AL5:AL30" si="2">COUNTIF(F5:AJ5,"A")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM5" s="5" t="s">
         <v>8</v>
@@ -5459,7 +5632,7 @@
       </c>
       <c r="AP5" s="3"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -5475,40 +5648,92 @@
       <c r="E6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="22"/>
-      <c r="AJ6" s="11"/>
+      <c r="F6" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="38"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R6" s="26"/>
+      <c r="S6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y6" s="26"/>
+      <c r="Z6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF6" s="26"/>
+      <c r="AG6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ6" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK6" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="2"/>
@@ -5523,7 +5748,7 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -5539,51 +5764,103 @@
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="22"/>
-      <c r="AJ7" s="11"/>
+      <c r="F7" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="38"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R7" s="26"/>
+      <c r="S7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y7" s="26"/>
+      <c r="Z7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF7" s="26"/>
+      <c r="AG7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ7" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK7" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -5599,53 +5876,105 @@
       <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="28"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="22"/>
-      <c r="AJ8" s="11"/>
+      <c r="F8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" s="38"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R8" s="26"/>
+      <c r="S8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y8" s="26"/>
+      <c r="Z8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF8" s="26"/>
+      <c r="AG8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ8" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK8" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM8" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="AN8" s="25"/>
-      <c r="AO8" s="25"/>
-      <c r="AP8" s="26"/>
+      <c r="AN8" s="32"/>
+      <c r="AO8" s="32"/>
+      <c r="AP8" s="33"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -5661,44 +5990,96 @@
       <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="22"/>
-      <c r="AJ9" s="11"/>
+      <c r="F9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="38"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R9" s="26"/>
+      <c r="S9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC9" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ9" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK9" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM9" s="5" t="s">
         <v>12</v>
@@ -5713,7 +6094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -5729,44 +6110,96 @@
       <c r="E10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="28"/>
-      <c r="AG10" s="11"/>
-      <c r="AH10" s="11"/>
-      <c r="AI10" s="22"/>
-      <c r="AJ10" s="11"/>
+      <c r="F10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J10" s="38"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R10" s="26"/>
+      <c r="S10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ10" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK10" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" s="5" t="s">
         <v>16</v>
@@ -5784,7 +6217,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -5800,62 +6233,114 @@
       <c r="E11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="28"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="28"/>
-      <c r="AG11" s="11"/>
-      <c r="AH11" s="11"/>
-      <c r="AI11" s="22"/>
-      <c r="AJ11" s="11"/>
+      <c r="F11" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="38"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R11" s="26"/>
+      <c r="S11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH11" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI11" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ11" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK11" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="AN11" s="12">
         <f>SUM(AK5:AK30)</f>
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="AO11" s="12">
         <f>SUM(AK5:AK30)</f>
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="AP11" s="12">
         <f>AN11+AO11</f>
-        <v>0</v>
+        <v>1134</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>8</v>
       </c>
@@ -5871,62 +6356,114 @@
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="28"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="28"/>
-      <c r="AG12" s="11"/>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="22"/>
-      <c r="AJ12" s="11"/>
+      <c r="F12" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" s="38"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R12" s="26"/>
+      <c r="S12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y12" s="26"/>
+      <c r="Z12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF12" s="26"/>
+      <c r="AG12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ12" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK12" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0</v>
+        <v>1.1477732793522266</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0</v>
+        <v>1.0384615384615385</v>
       </c>
       <c r="AP12" s="12">
         <f>AP11/AP10</f>
-        <v>0</v>
+        <v>1.0903846153846153</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -5942,40 +6479,92 @@
       <c r="E13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="28"/>
-      <c r="AG13" s="11"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="22"/>
-      <c r="AJ13" s="11"/>
+      <c r="F13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="38"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R13" s="26"/>
+      <c r="S13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ13" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK13" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="2"/>
@@ -5986,7 +6575,7 @@
       <c r="AO13" s="17"/>
       <c r="AP13" s="17"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -6002,51 +6591,103 @@
       <c r="E14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="28"/>
-      <c r="AG14" s="11"/>
-      <c r="AH14" s="11"/>
-      <c r="AI14" s="22"/>
-      <c r="AJ14" s="11"/>
+      <c r="F14" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H14" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="38"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R14" s="26"/>
+      <c r="S14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y14" s="26"/>
+      <c r="Z14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ14" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK14" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM14" s="19"/>
       <c r="AN14" s="19"/>
       <c r="AO14" s="19"/>
       <c r="AP14" s="19"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -6062,51 +6703,103 @@
       <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="28"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="22"/>
-      <c r="AJ15" s="11"/>
+      <c r="F15" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="J15" s="38"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R15" s="26"/>
+      <c r="S15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ15" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="AK15" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AL15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>12</v>
       </c>
@@ -6122,53 +6815,105 @@
       <c r="E16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="28"/>
-      <c r="AG16" s="11"/>
-      <c r="AH16" s="11"/>
-      <c r="AI16" s="22"/>
-      <c r="AJ16" s="11"/>
+      <c r="F16" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="38"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R16" s="26"/>
+      <c r="S16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y16" s="26"/>
+      <c r="Z16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ16" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK16" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="25"/>
-      <c r="AO16" s="25"/>
-      <c r="AP16" s="26"/>
+      <c r="AN16" s="32"/>
+      <c r="AO16" s="32"/>
+      <c r="AP16" s="33"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -6184,44 +6929,96 @@
       <c r="E17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="28"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="28"/>
-      <c r="AG17" s="11"/>
-      <c r="AH17" s="11"/>
-      <c r="AI17" s="22"/>
-      <c r="AJ17" s="11"/>
+      <c r="F17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="38"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R17" s="26"/>
+      <c r="S17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y17" s="26"/>
+      <c r="Z17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF17" s="26"/>
+      <c r="AG17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ17" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK17" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM17" s="5" t="s">
         <v>12</v>
@@ -6236,7 +7033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>14</v>
       </c>
@@ -6252,44 +7049,96 @@
       <c r="E18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="28"/>
-      <c r="AG18" s="11"/>
-      <c r="AH18" s="11"/>
-      <c r="AI18" s="22"/>
-      <c r="AJ18" s="11"/>
+      <c r="F18" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J18" s="38"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R18" s="26"/>
+      <c r="S18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y18" s="26"/>
+      <c r="Z18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC18" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD18" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF18" s="26"/>
+      <c r="AG18" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH18" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AI18" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ18" s="11" t="s">
+        <v>131</v>
+      </c>
       <c r="AK18" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL18" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM18" s="5" t="s">
         <v>16</v>
@@ -6307,7 +7156,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -6323,62 +7172,114 @@
       <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="22"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="22"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="22"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="28"/>
-      <c r="AG19" s="11"/>
-      <c r="AH19" s="11"/>
-      <c r="AI19" s="22"/>
-      <c r="AJ19" s="11"/>
+      <c r="F19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J19" s="38"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R19" s="26"/>
+      <c r="S19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y19" s="26"/>
+      <c r="Z19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF19" s="26"/>
+      <c r="AG19" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ19" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK19" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM19" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>494</v>
+        <v>-73</v>
       </c>
       <c r="AO19" s="12">
         <f>AO18-AO11</f>
-        <v>546</v>
+        <v>-21</v>
       </c>
       <c r="AP19" s="12">
         <f>AN19+AO19</f>
-        <v>1040</v>
+        <v>-94</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>16</v>
       </c>
@@ -6394,40 +7295,92 @@
       <c r="E20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="22"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="22"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="28"/>
-      <c r="AG20" s="11"/>
-      <c r="AH20" s="11"/>
-      <c r="AI20" s="22"/>
-      <c r="AJ20" s="11"/>
+      <c r="F20" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="38"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R20" s="26"/>
+      <c r="S20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF20" s="26"/>
+      <c r="AG20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ20" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK20" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL20" s="5">
         <f t="shared" si="2"/>
@@ -6438,18 +7391,18 @@
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>1</v>
+        <v>-0.14777327935222673</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>1</v>
+        <v>-3.8461538461538464E-2</v>
       </c>
       <c r="AP20" s="20">
         <f>AP19/AP18</f>
-        <v>1</v>
+        <v>-9.0384615384615383E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -6465,47 +7418,99 @@
       <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="28"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="11"/>
-      <c r="AD21" s="11"/>
-      <c r="AE21" s="11"/>
-      <c r="AF21" s="28"/>
-      <c r="AG21" s="11"/>
-      <c r="AH21" s="11"/>
-      <c r="AI21" s="22"/>
-      <c r="AJ21" s="11"/>
+      <c r="F21" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21" s="38"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R21" s="26"/>
+      <c r="S21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y21" s="26"/>
+      <c r="Z21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF21" s="26"/>
+      <c r="AG21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH21" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ21" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK21" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL21" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>18</v>
       </c>
@@ -6521,47 +7526,99 @@
       <c r="E22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="28"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="28"/>
-      <c r="AG22" s="11"/>
-      <c r="AH22" s="11"/>
-      <c r="AI22" s="22"/>
-      <c r="AJ22" s="11"/>
+      <c r="F22" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="38"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R22" s="26"/>
+      <c r="S22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y22" s="26"/>
+      <c r="Z22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF22" s="26"/>
+      <c r="AG22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ22" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK22" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL22" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -6575,47 +7632,99 @@
       <c r="E23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="22"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="28"/>
-      <c r="AG23" s="11"/>
-      <c r="AH23" s="11"/>
-      <c r="AI23" s="22"/>
-      <c r="AJ23" s="11"/>
+      <c r="F23" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="38"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R23" s="26"/>
+      <c r="S23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y23" s="26"/>
+      <c r="Z23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF23" s="26"/>
+      <c r="AG23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ23" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK23" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL23" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>20</v>
       </c>
@@ -6629,47 +7738,99 @@
       <c r="E24" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="22"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="22"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="28"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="22"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="11"/>
-      <c r="AD24" s="11"/>
-      <c r="AE24" s="11"/>
-      <c r="AF24" s="28"/>
-      <c r="AG24" s="11"/>
-      <c r="AH24" s="11"/>
-      <c r="AI24" s="22"/>
-      <c r="AJ24" s="11"/>
+      <c r="F24" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="38"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R24" s="26"/>
+      <c r="S24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y24" s="26"/>
+      <c r="Z24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE24" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF24" s="26"/>
+      <c r="AG24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ24" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK24" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL24" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -6683,47 +7844,99 @@
       <c r="E25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="22"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="11"/>
-      <c r="AD25" s="11"/>
-      <c r="AE25" s="11"/>
-      <c r="AF25" s="28"/>
-      <c r="AG25" s="11"/>
-      <c r="AH25" s="11"/>
-      <c r="AI25" s="22"/>
-      <c r="AJ25" s="11"/>
+      <c r="F25" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="38"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R25" s="26"/>
+      <c r="S25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y25" s="26"/>
+      <c r="Z25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE25" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF25" s="26"/>
+      <c r="AG25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ25" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK25" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>22</v>
       </c>
@@ -6739,47 +7952,99 @@
       <c r="E26" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="22"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="22"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="28"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="11"/>
-      <c r="AD26" s="11"/>
-      <c r="AE26" s="11"/>
-      <c r="AF26" s="28"/>
-      <c r="AG26" s="11"/>
-      <c r="AH26" s="11"/>
-      <c r="AI26" s="22"/>
-      <c r="AJ26" s="11"/>
+      <c r="F26" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J26" s="38"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R26" s="26"/>
+      <c r="S26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y26" s="26"/>
+      <c r="Z26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF26" s="26"/>
+      <c r="AG26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ26" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK26" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -6795,47 +8060,99 @@
       <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="22"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="22"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="11"/>
-      <c r="AD27" s="11"/>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="28"/>
-      <c r="AG27" s="11"/>
-      <c r="AH27" s="11"/>
-      <c r="AI27" s="22"/>
-      <c r="AJ27" s="11"/>
+      <c r="F27" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="38"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R27" s="26"/>
+      <c r="S27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y27" s="26"/>
+      <c r="Z27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF27" s="26"/>
+      <c r="AG27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ27" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK27" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL27" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>24</v>
       </c>
@@ -6849,47 +8166,99 @@
       <c r="E28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="22"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="11"/>
-      <c r="AD28" s="11"/>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="28"/>
-      <c r="AG28" s="11"/>
-      <c r="AH28" s="11"/>
-      <c r="AI28" s="22"/>
-      <c r="AJ28" s="11"/>
+      <c r="F28" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J28" s="38"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R28" s="26"/>
+      <c r="S28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF28" s="26"/>
+      <c r="AG28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ28" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK28" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL28" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>25</v>
       </c>
@@ -6903,47 +8272,99 @@
       <c r="E29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="22"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="11"/>
-      <c r="AA29" s="22"/>
-      <c r="AB29" s="11"/>
-      <c r="AC29" s="11"/>
-      <c r="AD29" s="11"/>
-      <c r="AE29" s="11"/>
-      <c r="AF29" s="28"/>
-      <c r="AG29" s="11"/>
-      <c r="AH29" s="11"/>
-      <c r="AI29" s="22"/>
-      <c r="AJ29" s="11"/>
+      <c r="F29" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I29" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J29" s="38"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R29" s="26"/>
+      <c r="S29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="U29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="V29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y29" s="26"/>
+      <c r="Z29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AD29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF29" s="26"/>
+      <c r="AG29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ29" s="11" t="s">
+        <v>130</v>
+      </c>
       <c r="AK29" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL29" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>26</v>
       </c>
@@ -6957,48 +8378,101 @@
       <c r="E30" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="22"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="11"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="11"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="29"/>
-      <c r="Z30" s="11"/>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="11"/>
-      <c r="AC30" s="11"/>
-      <c r="AD30" s="11"/>
-      <c r="AE30" s="11"/>
-      <c r="AF30" s="29"/>
-      <c r="AG30" s="11"/>
-      <c r="AH30" s="11"/>
-      <c r="AI30" s="22"/>
-      <c r="AJ30" s="11"/>
+      <c r="F30" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J30" s="39"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q30" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R30" s="27"/>
+      <c r="S30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y30" s="27"/>
+      <c r="Z30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD30" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE30" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF30" s="27"/>
+      <c r="AG30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ30" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK30" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL30" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="J5:J30"/>
     <mergeCell ref="AM8:AP8"/>
     <mergeCell ref="AM16:AP16"/>
     <mergeCell ref="A2:AJ2"/>
@@ -7019,12 +8493,12 @@
   <conditionalFormatting sqref="B5:B30">
     <cfRule type="duplicateValues" dxfId="12" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:M5 R5 T5 V5 Y5 AA5 AF5 AI5 N5:Q30 S5:S30 U5:U30 W5:X30 Z5:Z30 AB5:AE30 AG5:AH30 AJ5:AJ30 G6:J30 L6:L30 F4:AJ4">
+  <conditionalFormatting sqref="F6:I30 L6:Q30 S6:X30 Z6:AE30 F4:AJ5 AG6:AJ30">
     <cfRule type="expression" dxfId="11" priority="15">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:M5 R5 T5 V5 Y5 AA5 AF5 AI5 N5:Q30 S5:S30 U5:U30 W5:X30 Z5:Z30 AB5:AE30 AG5:AH30 AJ5:AJ30 G6:J30 L6:L30">
+  <conditionalFormatting sqref="F6:I30 L6:Q30 S6:X30 Z6:AE30 F5:AJ5 AG6:AJ30">
     <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -7035,7 +8509,7 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:AJ4 F5:M5 R5 T5 V5 Y5 AA5 AF5 AI5 N5:Q30 S5:S30 U5:U30 W5:X30 Z5:Z30 AB5:AE30 AG5:AH30 AJ5:AJ30 G6:J30 L6:L30">
+  <conditionalFormatting sqref="F6:I30 L6:Q30 S6:X30 Z6:AE30 F3:AJ5 AG6:AJ30">
     <cfRule type="expression" dxfId="7" priority="16">
       <formula>F$3="Sun"</formula>
     </cfRule>
